--- a/J30/Output_files/Original_Order_Search.xlsx
+++ b/J30/Output_files/Original_Order_Search.xlsx
@@ -425,91 +425,76 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Plant</t>
+          <t>OrderId</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>OrderType</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>OrderId</t>
+          <t>LoadingGroup</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>OrderType</t>
+          <t>Shipment</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>LoadingGroup</t>
+          <t>Stop</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>PickupStartDate</t>
+          <t>Carrier</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>PickupEndDate</t>
+          <t>HUB</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>DeliveryStartDate</t>
+          <t>SUB_HUB</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>DeliveryEndDate</t>
+          <t>PrePackCode</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>IDPInstruction</t>
+          <t>ItemName</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>PrePackGroupCode</t>
+          <t>Qty</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>ItemName</t>
+          <t>ServiceTypeID</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Qty</t>
+          <t>ProvidedServiceId</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Sequence</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>ServiceTypeID</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>ProvidedServiceId</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ServiceUomId</t>
         </is>
@@ -518,456 +503,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1081</t>
+          <t>0160561600</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>Z003</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0160124809</t>
+          <t>0227_ＳＤＦＳ天久店_FW_8019</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Z004</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>122845</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>122845_2</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>February 20, 2026 09:00:00 AM GMT+9</t>
+          <t>NITA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>February 20, 2026 09:00:00 AM GMT+9</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>February 24, 2026 08:00:00 PM GMT+9</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>February 25, 2026 05:00:00 AM GMT+9</t>
-        </is>
-      </c>
+          <t>H723</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>２／２４＠ＮＴ＿Ｒ＿夜</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>OR</t>
-        </is>
+          <t>415082-002-4Y</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>6</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>263238-100-L/XL</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
-        <v>6</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
           <t>VAS</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>CTL</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>oLPN</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>0160124810</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Z004</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>February 20, 2026 09:00:00 AM GMT+9</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>February 20, 2026 09:00:00 AM GMT+9</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>February 24, 2026 08:00:00 PM GMT+9</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>February 25, 2026 05:00:00 AM GMT+9</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>２／２４＠ＮＴ＿Ｒ＿夜</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>343738-031-1.5Y</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>6</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>VAS</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>CTL</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>oLPN</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>0160504201</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Z004</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>February 20, 2026 09:00:00 AM GMT+9</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>February 20, 2026 09:00:00 AM GMT+9</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>February 24, 2026 01:00:00 PM GMT+9</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>February 24, 2026 07:59:00 PM GMT+9</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>２／２４＠ＰＭ＿ＮＥＷ</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>343738-031-1.5Y</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>6</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>VAS</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>CTL</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>oLPN</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0160544800</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Z004</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>February 20, 2026 09:00:00 AM GMT+9</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>February 20, 2026 09:00:00 AM GMT+9</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>February 24, 2026 01:00:00 PM GMT+9</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>February 24, 2026 07:59:00 PM GMT+9</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>２／２４＠ＰＭ＿Ｒ＿夜</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>PR</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>343738-031-1.5Y</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>6</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>VAS</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>CTL</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>oLPN</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0160545000</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Z004</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>February 20, 2026 09:00:00 AM GMT+9</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>February 20, 2026 09:00:00 AM GMT+9</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>February 24, 2026 09:00:00 AM GMT+9</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>February 24, 2026 09:00:00 AM GMT+9</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>２／２４＠９：００＿Ｒ＿夜</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>343738-031-1.5Y</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>6</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>VAS</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>CTL</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>oLPN</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0160545200</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Z004</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>February 20, 2026 09:00:00 AM GMT+9</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>February 20, 2026 09:00:00 AM GMT+9</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>February 24, 2026 08:00:00 PM GMT+9</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>February 25, 2026 05:00:00 AM GMT+9</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>２／２４＠ＮＴ＿Ｒ＿夜</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>343738-031-1.5Y</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>18</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>VAS</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>CTL</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>oLPN</t>
         </is>

--- a/J30/Output_files/Original_Order_Search.xlsx
+++ b/J30/Output_files/Original_Order_Search.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OriginalOrder" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ParentOrderLine" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,131 +436,44 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>OrderType</t>
+          <t>Original_Order_id</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>LoadingGroup</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Shipment</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Carrier</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>HUB</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>SUB_HUB</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>PrePackCode</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>ItemName</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Qty</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>ServiceTypeID</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>ProvidedServiceId</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>ServiceUomId</t>
+          <t>WaveID</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0160561600</t>
+          <t>810000622</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Z003</t>
+          <t>0160443601</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0227_ＳＤＦＳ天久店_FW_8019</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>122845</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>122845_2</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>NITA</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>H723</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>415082-002-4Y</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>6</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>VAS</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>CTL</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>oLPN</t>
-        </is>
-      </c>
+          <t>W02272026000000000006</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>810000623</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0160061806</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/J30/Output_files/Original_Order_Search.xlsx
+++ b/J30/Output_files/Original_Order_Search.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ParentOrderLine" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OriginalOrder" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,44 +436,265 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Original_Order_id</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>WaveID</t>
+          <t>LoadingGroup</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>ShipTo</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Shipment</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Carrier</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>HUB</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>SUB_HUB</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>PrePackCode</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>ItemName</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Sequence</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>ServiceTypeID</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ProvidedServiceId</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ServiceUomId</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>810000622</t>
+          <t>0160105604</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0160443601</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>W02272026000000000006</t>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0005028551</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>H888</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>SH3-12-5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>AJ7566-085-S</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>VAS</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>CTL</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>oLPN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>810000623</t>
+          <t>0160412602</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0160061806</t>
+          <t>Draft</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0005028551</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>H888</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>SH3-12-5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>AJ7566-085-S</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>6</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>VAS</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>CTL</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>oLPN</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>0160412602</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0005028551</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>H888</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>SH3-12-5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>AJ7566-085-S</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>6</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>VAS</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>LBL</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>ITEM</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/J30/Output_files/Original_Order_Search.xlsx
+++ b/J30/Output_files/Original_Order_Search.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OriginalOrder" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ParentOrderLine" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,265 +437,729 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>OrderType</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>LoadingGroup</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>ShipTo</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Shipment</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Carrier</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>HUB</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>SUB_HUB</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>PrePackCode</t>
-        </is>
-      </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>PickupEndDate</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>ItemName</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Qty</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Sequence</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>ServiceTypeID</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>ProvidedServiceId</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>ServiceUomId</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0160105604</t>
+          <t>0160174405</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Draft</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>Z033</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Loaded</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0005028551</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+          <t>SAGA_0324_H__3_E</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0005054147</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>20260324_MIX_20260320174907</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>20260324_MIX_20260320174907_2</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>H888</t>
+          <t>SAGA</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SH3-12-5</t>
+          <t>H841</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>352-514</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>March 24, 2026 10:00:00 PM GMT+9</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>AJ7566-085-S</t>
         </is>
       </c>
-      <c r="L2" t="n">
-        <v>6</v>
-      </c>
       <c r="M2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>VAS</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>CTL</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>oLPN</t>
-        </is>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0160412602</t>
+          <t>0160191040</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Draft</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>Z033</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Allocated</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0005028551</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+          <t>SAGA_0324_H__3_E</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0005054147</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>20260324_MIX_20260320174907</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>20260324_MIX_20260320174907_2</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>H888</t>
+          <t>SAGA</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SH3-12-5</t>
+          <t>H841</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>352-514</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>March 24, 2026 10:00:00 PM GMT+9</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>AJ7566-085-S</t>
         </is>
       </c>
-      <c r="L3" t="n">
-        <v>6</v>
-      </c>
       <c r="M3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>VAS</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>CTL</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>oLPN</t>
-        </is>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0160412602</t>
+          <t>0160191041</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Draft</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>Z033</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Loaded</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0005028551</t>
+          <t>SAGA_0324_H__3_E</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0005054147</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>20260324_MIX_20260320174907</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>20260324_MIX_20260320174907_2</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>SAGA</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>H841</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>352-514</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>March 24, 2026 10:00:00 PM GMT+9</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>AJ7566-085-S</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>0160191042</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Z033</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Loaded</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SAGA_0324_H_J3_E</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0005054147</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>20260324_MIX_20260320173413</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>20260324_MIX_20260320173413_2</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>SAGA</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>H841</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>032-101</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>March 25, 2026 12:00:00 AM GMT+9</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>AJ7566-085-S</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>0160191043</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Z033</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Loaded</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>SAGA_0324_H_J3_E</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0005054147</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>20260324_MIX_20260320173413</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>20260324_MIX_20260320173413_2</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>SAGA</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>H841</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>032-101</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>March 25, 2026 12:00:00 AM GMT+9</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>AJ7566-085-S</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>0160550424</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Z033</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Packed</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SAGA_0324_H__3_E</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0005054147</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>20260324_MIX_20260320174907</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>20260324_MIX_20260320174907_2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>SAGA</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>H841</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>352-514</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>March 24, 2026 10:00:00 PM GMT+9</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>AJ7566-085-S</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>0160599218</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Z033</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Packed</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SAGA_0324_H__3_E</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0005054147</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>20260324_MIX_20260320174907</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>20260324_MIX_20260320174907_2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>SAGA</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>H841</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>352-514</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>March 24, 2026 10:00:00 PM GMT+9</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>AJ7566-085-S</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>OrderId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Original_Order_id</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>WaveID</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>SpurID</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>810001051</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LOADED</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0160191042</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>W03202026000000000010</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>6222000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>810001052</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LOADED</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0160191043</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>W03202026000000000010</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>6222000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>810001055</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ALLOCATED</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0160191040</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>W03202026000000000010</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>H888</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>SH3-12-5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>OR</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>AJ7566-085-S</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>6</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>VAS</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>LBL</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>ITEM</t>
-        </is>
-      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>810001056</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LOADED</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0160191041</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>W03202026000000000010</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>810001057</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LOADED</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0160174405</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>W03202026000000000010</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>810001058</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PACKED</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0160550424</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>W03202026000000000010</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>810001059</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PACKED</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0160599218</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>W03202026000000000010</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/J30/Output_files/Original_Order_Search.xlsx
+++ b/J30/Output_files/Original_Order_Search.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,60 +437,25 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>OrderType</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>LoadingGroup</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>LoadingGroup</t>
+          <t>AssignedHub</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ShipTo</t>
+          <t>ItemName</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Shipment</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Carrier</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>HUB</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>SUB_HUB</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>PickupEndDate</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>ItemName</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
@@ -499,455 +464,90 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0160174405</t>
+          <t>0576316206</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Z033</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Loaded</t>
+          <t>0404_SAGA_H_X3_C_08493</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SAGA_0324_H__3_E</t>
+          <t>H_X3</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0005054147</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>20260324_MIX_20260320174907</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>20260324_MIX_20260320174907_2</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>SAGA</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>H841</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>352-514</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>March 24, 2026 10:00:00 PM GMT+9</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>AJ7566-085-S</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
+          <t>343880-090-6</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0160191040</t>
+          <t>0576316207</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Z033</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Allocated</t>
+          <t>0404_SAGA_H_X3_C_08493</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SAGA_0324_H__3_E</t>
+          <t>H_X3</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0005054147</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>20260324_MIX_20260320174907</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>20260324_MIX_20260320174907_2</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SAGA</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>H841</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>352-514</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>March 24, 2026 10:00:00 PM GMT+9</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>AJ7566-085-S</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>4</v>
+          <t>DA5718-010-M</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0160191041</t>
+          <t>0576321102</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Z033</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Loaded</t>
+          <t>0406_SAGA_H__3_C_08492</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SAGA_0324_H__3_E</t>
+          <t>H__3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0005054147</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>20260324_MIX_20260320174907</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>20260324_MIX_20260320174907_2</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>SAGA</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>H841</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>352-514</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>March 24, 2026 10:00:00 PM GMT+9</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>AJ7566-085-S</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>0160191042</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Z033</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Loaded</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>SAGA_0324_H_J3_E</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0005054147</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>20260324_MIX_20260320173413</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>20260324_MIX_20260320173413_2</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>SAGA</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>H841</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>032-101</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>March 25, 2026 12:00:00 AM GMT+9</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>AJ7566-085-S</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>0160191043</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Z033</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Loaded</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>SAGA_0324_H_J3_E</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0005054147</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>20260324_MIX_20260320173413</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>20260324_MIX_20260320173413_2</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>SAGA</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>H841</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>032-101</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>March 25, 2026 12:00:00 AM GMT+9</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>AJ7566-085-S</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>0160550424</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Z033</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Packed</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>SAGA_0324_H__3_E</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0005054147</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>20260324_MIX_20260320174907</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>20260324_MIX_20260320174907_2</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>SAGA</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>H841</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>352-514</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>March 24, 2026 10:00:00 PM GMT+9</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>AJ7566-085-S</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>0160599218</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Z033</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Packed</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>SAGA_0324_H__3_E</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0005054147</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>20260324_MIX_20260320174907</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>20260324_MIX_20260320174907_2</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>SAGA</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>H841</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>352-514</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>March 24, 2026 10:00:00 PM GMT+9</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>AJ7566-085-S</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
+          <t>DA5718-010-M</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -962,7 +562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -995,171 +595,83 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>810001051</t>
+          <t>810001358</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LOADED</t>
+          <t>SHIPPED</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0160191042</t>
+          <t>0576321102</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>W03202026000000000010</t>
+          <t>W04022026000000000005</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>6222000000</t>
+          <t>6205000000</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>810001052</t>
+          <t>810001360</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LOADED</t>
+          <t>SHIPPED</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0160191043</t>
+          <t>0576316207</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>W03202026000000000010</t>
+          <t>W04022026000000000005</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>6222000000</t>
+          <t>6205000000</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>810001055</t>
+          <t>810001360</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ALLOCATED</t>
+          <t>SHIPPED</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0160191040</t>
+          <t>0576316206</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>W03202026000000000010</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>810001056</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>LOADED</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0160191041</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>W03202026000000000010</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>810001057</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>LOADED</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0160174405</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>W03202026000000000010</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>810001058</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>PACKED</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0160550424</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>W03202026000000000010</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>810001059</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>PACKED</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>0160599218</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>W03202026000000000010</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
+          <t>W04022026000000000005</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>6205000000</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/J30/Output_files/Original_Order_Search.xlsx
+++ b/J30/Output_files/Original_Order_Search.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,108 +447,145 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>ServiceLvl</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>AssignedHub</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>CRD</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ItemName</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Qty</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>FullPrice</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>DiscountPrice</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>GiftBag</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExternalGiftBagPrice</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ShippingCharge</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0576316206</t>
+          <t>0576356400</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Allocated</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0404_SAGA_H_X3_C_08493</t>
+          <t>0414_SAGA_H_12_C_08561</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>H_X3</t>
+          <t>STD</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>H_12</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-04-14T00:00:00</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>343880-090-6</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="H2" t="n">
         <v>2</v>
+      </c>
+      <c r="I2" t="n">
+        <v>5730</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0576316207</t>
+          <t>0576356401</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Allocated</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0404_SAGA_H_X3_C_08493</t>
+          <t>0414_SAGA_H_12_E_08563</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>H_X3</t>
+          <t>STD</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>DA5718-010-M</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
+          <t>H_12</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-04-14T00:00:00</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>AR4999-101-L</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>0576321102</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Shipped</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>0406_SAGA_H__3_C_08492</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>H__3</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>DA5718-010-M</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
+      <c r="I3" t="n">
+        <v>5730</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -562,7 +599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -595,79 +632,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>810001358</t>
+          <t>810001465</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SHIPPED</t>
+          <t>ALLOCATED</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0576321102</t>
+          <t>0576356400</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>W04022026000000000005</t>
+          <t>W04072026000000000015</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>6205000000</t>
+          <t>6206000000</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>810001360</t>
+          <t>810001467</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SHIPPED</t>
+          <t>ALLOCATED</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0576316207</t>
+          <t>0576356401</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>W04022026000000000005</t>
+          <t>W04072026000000000015</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
-        <is>
-          <t>6205000000</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>810001360</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>SHIPPED</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>0576316206</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>W04022026000000000005</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
         <is>
           <t>6205000000</t>
         </is>

--- a/J30/Output_files/Original_Order_Search.xlsx
+++ b/J30/Output_files/Original_Order_Search.xlsx
@@ -499,7 +499,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0576356400</t>
+          <t>0576379600</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -509,43 +509,32 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0414_SAGA_H_12_C_08561</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>STD</t>
+          <t>0415_ＺＯＺＯ_EQ_8611</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>H_12</t>
+          <t>H731</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-14T00:00:00</t>
+          <t>2026-04-15T00:00:00</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>343880-090-6</t>
+          <t>DA5718-010-M</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I2" t="n">
-        <v>5730</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0576356401</t>
+          <t>0576379601</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -555,37 +544,26 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0414_SAGA_H_12_E_08563</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>STD</t>
+          <t>0415_ＺＯＺＯ_FW_8610</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>H_12</t>
+          <t>H731</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-14T00:00:00</t>
+          <t>2026-04-15T00:00:00</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>AR4999-101-L</t>
+          <t>343880-090-6</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" t="n">
-        <v>5730</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -632,7 +610,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>810001465</t>
+          <t>810001526</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -642,24 +620,24 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0576356400</t>
+          <t>0576379601</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>W04072026000000000015</t>
+          <t>W04092026000000000021</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>6206000000</t>
+          <t>6207000000</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>810001467</t>
+          <t>810001527</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -669,17 +647,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0576356401</t>
+          <t>0576379600</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>W04072026000000000015</t>
+          <t>W04092026000000000021</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>6205000000</t>
+          <t>6206000000</t>
         </is>
       </c>
     </row>

--- a/J30/Output_files/Original_Order_Search.xlsx
+++ b/J30/Output_files/Original_Order_Search.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:V2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,133 +437,181 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>OrderType</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>LoadingGroup</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>ShipTo</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Shipment</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Carrier</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>ServiceLvl</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>AssignedHub</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>CRD</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>HUB</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>SUB_HUB</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>ItemName</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>FullPrice</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>DiscountPrice</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>GiftBag</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>ExternalGiftBagPrice</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ShippingCharge</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Sequence</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>ServiceTypeID</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>ProvidedServiceId</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>ServiceUomId</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>PONumber</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0576379600</t>
+          <t>0576443200</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Allocated</t>
+          <t>Z005</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0415_ＺＯＺＯ_EQ_8611</t>
+          <t>Shipped</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0429_ＺＯＺＯ_AP_8887</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>0005079567</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>123391</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>PLUS</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>H731</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2026-04-15T00:00:00</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>DA5718-010-M</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>0576379601</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Allocated</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>0415_ＺＯＺＯ_FW_8610</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>H731</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-04-15T00:00:00</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>343880-090-6</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>6</v>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>706510-306-S/M</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>10</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>VAS</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>ZPL</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>oLPN</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>5221774</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -577,7 +625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -610,54 +658,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>810001526</t>
+          <t>810001860</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ALLOCATED</t>
+          <t>SHIPPED</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0576379601</t>
+          <t>0576443200</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>W04092026000000000021</t>
+          <t>W04232026000000000010</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>6207000000</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>810001527</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ALLOCATED</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>0576379600</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>W04092026000000000021</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>6206000000</t>
+          <t>6405000000</t>
         </is>
       </c>
     </row>
